--- a/artfynd/A 9166-2022 artfynd.xlsx
+++ b/artfynd/A 9166-2022 artfynd.xlsx
@@ -5121,7 +5121,7 @@
         <v>99677166</v>
       </c>
       <c r="B42" t="n">
-        <v>5179</v>
+        <v>5182</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 9166-2022 artfynd.xlsx
+++ b/artfynd/A 9166-2022 artfynd.xlsx
@@ -5149,11 +5149,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bengtsfors, Dls</t>

--- a/artfynd/A 9166-2022 artfynd.xlsx
+++ b/artfynd/A 9166-2022 artfynd.xlsx
@@ -5121,7 +5121,7 @@
         <v>99677166</v>
       </c>
       <c r="B42" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
